--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU46"/>
+  <dimension ref="A1:AU47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46193.70833333334</v>
+        <v>46193.6875</v>
       </c>
     </row>
     <row r="32">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46193.77083333334</v>
+        <v>46193.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46193.79166666666</v>
+        <v>46193.77083333334</v>
       </c>
     </row>
     <row r="34">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46193.83333333334</v>
+        <v>46193.79166666666</v>
       </c>
     </row>
     <row r="37">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>46193.85416666666</v>
+        <v>46193.83333333334</v>
       </c>
     </row>
     <row r="40">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46193.875</v>
+        <v>46193.85416666666</v>
       </c>
     </row>
     <row r="41">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="AU42" s="3" t="n">
-        <v>46193.89583333334</v>
+        <v>46193.875</v>
       </c>
     </row>
     <row r="43">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46193.95833333334</v>
+        <v>46193.89583333334</v>
       </c>
     </row>
     <row r="45">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46193.97916666666</v>
+        <v>46193.95833333334</v>
       </c>
     </row>
     <row r="46">
@@ -7824,6 +7824,165 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
+        <v>46193.97916666666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="3" t="n">
         <v>46193.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P39" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P39" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5981,34 +5981,34 @@
         <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
         <v>2.15</v>
@@ -6017,19 +6017,19 @@
         <v>1.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU47"/>
+  <dimension ref="A1:AU48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5289,27 +5289,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>3.79</v>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46193.6875</v>
+        <v>46193.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O32" t="n">
         <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46193.70833333334</v>
+        <v>46193.6875</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46193.77083333334</v>
+        <v>46193.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5809,17 +5809,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46193.79166666666</v>
+        <v>46193.77083333334</v>
       </c>
     </row>
     <row r="35">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6243,12 +6243,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46193.83333333334</v>
+        <v>46193.79166666666</v>
       </c>
     </row>
     <row r="38">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6617,55 +6617,55 @@
         <v>1.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46193.85416666666</v>
+        <v>46193.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46193.875</v>
+        <v>46193.85416666666</v>
       </c>
     </row>
     <row r="42">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46193.89583333334</v>
+        <v>46193.875</v>
       </c>
     </row>
     <row r="44">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46193.95833333334</v>
+        <v>46193.89583333334</v>
       </c>
     </row>
     <row r="46">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46193.97916666666</v>
+        <v>46193.95833333334</v>
       </c>
     </row>
     <row r="47">
@@ -7848,141 +7848,300 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="3" t="n">
+        <v>46193.97916666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Orange County SC</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>2.18</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O48" t="n">
         <v>3.24</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P48" t="n">
         <v>3.02</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="Q48" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA48" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AB48" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" s="3" t="n">
+      <c r="AC48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="3" t="n">
         <v>46193.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O31" t="n">
-        <v>3.79</v>
+        <v>2.86</v>
       </c>
       <c r="P31" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="R38" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="S38" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.34</v>
+        <v>3.98</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.34</v>
+        <v>2.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O40" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P40" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="S40" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="U40" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W40" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.34</v>
+        <v>3.98</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.34</v>
+        <v>2.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="S40" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T40" t="n">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.98</v>
+        <v>3.34</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.71</v>
+        <v>3.34</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.63</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T38" t="n">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="U38" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="V38" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.98</v>
+        <v>3.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.71</v>
+        <v>3.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>5.63</v>
       </c>
       <c r="O40" t="n">
-        <v>3.08</v>
+        <v>4.6</v>
       </c>
       <c r="P40" t="n">
-        <v>3.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="S40" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="U40" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W40" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.34</v>
+        <v>3.98</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.34</v>
+        <v>2.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.41</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
-        <v>3.07</v>
+        <v>3.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="V19" t="n">
         <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,68 +5014,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O31" t="n">
-        <v>3.79</v>
+        <v>2.86</v>
       </c>
       <c r="P31" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="R36" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S36" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T36" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.72</v>
+        <v>3.78</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,80 +6290,80 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.45</v>
       </c>
-      <c r="O37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF37" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK37" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4073,7 +4073,7 @@
         <v>14.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
         <v>2.43</v>
@@ -4097,13 +4097,13 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
         <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
         <v>2.2</v>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,68 +5014,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="R36" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
         <v>2.64</v>
       </c>
       <c r="P28" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>2.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,65 +5972,65 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="R35" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U35" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC35" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.63</v>
+        <v>2.19</v>
       </c>
       <c r="O40" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.8</v>
+        <v>2.78</v>
       </c>
       <c r="R40" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="S40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.23</v>
       </c>
-      <c r="T40" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="Z40" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.08</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O47" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="P47" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="R47" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T47" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U47" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF47" t="n">
         <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU48"/>
+  <dimension ref="A1:AU47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46193.66666666666</v>
+        <v>46193.6875</v>
       </c>
     </row>
     <row r="32">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O32" t="n">
         <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46193.6875</v>
+        <v>46193.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46193.70833333334</v>
+        <v>46193.77083333334</v>
       </c>
     </row>
     <row r="34">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46193.77083333334</v>
+        <v>46193.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S35" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
         <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>3.78</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6243,12 +6243,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>5.55</v>
       </c>
       <c r="O37" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="P37" t="n">
-        <v>2.98</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.77</v>
+        <v>5.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="S37" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="T37" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="U37" t="n">
         <v>2.5</v>
       </c>
-      <c r="U37" t="n">
-        <v>2.88</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.9</v>
+        <v>3.98</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.11</v>
+        <v>1.64</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.78</v>
+        <v>2.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46193.79166666666</v>
+        <v>46193.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O39" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q39" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="W39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.23</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.21</v>
-      </c>
       <c r="Z39" t="n">
-        <v>3.98</v>
+        <v>3.42</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="O40" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46193.83333333334</v>
+        <v>46193.85416666666</v>
       </c>
     </row>
     <row r="41">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46193.85416666666</v>
+        <v>46193.875</v>
       </c>
     </row>
     <row r="42">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46193.875</v>
+        <v>46193.89583333334</v>
       </c>
     </row>
     <row r="44">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46193.89583333334</v>
+        <v>46193.95833333334</v>
       </c>
     </row>
     <row r="46">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46193.95833333334</v>
+        <v>46193.97916666666</v>
       </c>
     </row>
     <row r="47">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7983,165 +7983,6 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46193.97916666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" s="3" t="n">
         <v>46193.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,65 +5972,65 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="R35" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U35" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC35" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O37" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="P37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V37" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q37" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.23</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.21</v>
-      </c>
       <c r="Z37" t="n">
-        <v>3.98</v>
+        <v>3.42</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.37</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.49</v>
+        <v>2.83</v>
       </c>
       <c r="R3" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="S3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.22</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>4.37</v>
       </c>
       <c r="O4" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.83</v>
+        <v>4.49</v>
       </c>
       <c r="R4" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R21" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V21" t="n">
         <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O38" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="P38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S38" t="n">
+      <c r="W38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.23</v>
       </c>
-      <c r="T38" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.21</v>
-      </c>
       <c r="Z38" t="n">
-        <v>3.98</v>
+        <v>3.42</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>4.37</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.83</v>
+        <v>4.74</v>
       </c>
       <c r="R3" t="n">
-        <v>2.11</v>
+        <v>2.41</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.37</v>
+        <v>2.23</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>2.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.49</v>
+        <v>2.82</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.22</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1682,7 +1682,7 @@
         <v>2.19</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
         <v>3.15</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
         <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.05</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AD21" t="n">
         <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4073,25 +4073,25 @@
         <v>14.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R23" t="n">
         <v>2.43</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
@@ -4865,7 +4865,7 @@
         <v>2.64</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5822,10 +5822,10 @@
         <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>1.42</v>
@@ -5834,7 +5834,7 @@
         <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V34" t="n">
         <v>1.36</v>
@@ -5843,34 +5843,34 @@
         <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z34" t="n">
         <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="AD34" t="n">
         <v>1.19</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF34" t="n">
         <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,65 +6449,65 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.19</v>
+        <v>5.55</v>
       </c>
       <c r="O38" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="P38" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.78</v>
+        <v>5.55</v>
       </c>
       <c r="R38" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="S38" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AB38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC38" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
         <v>3.18</v>
@@ -7892,13 +7892,13 @@
         <v>2.58</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S47" t="n">
         <v>1.32</v>
       </c>
       <c r="T47" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
         <v>2.5</v>
@@ -7919,16 +7919,16 @@
         <v>4.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC47" t="n">
         <v>2.71</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE47" t="n">
         <v>1.1</v>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK47" t="n">
         <v>1.65</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.37</v>
+        <v>2.23</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>2.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.74</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.23</v>
+        <v>4.37</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.87</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.82</v>
+        <v>4.74</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.12</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O38" t="n">
-        <v>4.15</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.49</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.98</v>
+        <v>3.14</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.19</v>
+        <v>5.55</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>4.15</v>
       </c>
       <c r="P38" t="n">
-        <v>2.95</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.86</v>
+        <v>5.8</v>
       </c>
       <c r="R38" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="S38" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="T38" t="n">
-        <v>2.93</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O39" t="n">
-        <v>4.15</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.55</v>
+        <v>2.86</v>
       </c>
       <c r="R39" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="S39" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.54</v>
+        <v>2.93</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
         <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.98</v>
+        <v>3.14</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.23</v>
+        <v>4.37</v>
       </c>
       <c r="O3" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.87</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.82</v>
+        <v>4.74</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.52</v>
+        <v>1.12</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.37</v>
+        <v>2.23</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>2.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.74</v>
+        <v>2.82</v>
       </c>
       <c r="R4" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.05</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.88</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>3.98</v>
       </c>
       <c r="AD19" t="n">
         <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5822,10 +5822,10 @@
         <v>2.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S34" t="n">
         <v>1.42</v>
@@ -5834,7 +5834,7 @@
         <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="V34" t="n">
         <v>1.36</v>
@@ -5867,7 +5867,7 @@
         <v>1.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG34" t="n">
         <v>1.86</v>
@@ -5886,7 +5886,7 @@
         <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>3.46</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.37</v>
+        <v>5.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.74</v>
+        <v>5.43</v>
       </c>
       <c r="R3" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U3" t="n">
         <v>2.15</v>
@@ -911,7 +911,7 @@
         <v>1.61</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -920,13 +920,13 @@
         <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC3" t="n">
         <v>2.15</v>
@@ -938,10 +938,10 @@
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,37 +1043,37 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.87</v>
+        <v>2.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.82</v>
+        <v>3.53</v>
       </c>
       <c r="R4" t="n">
         <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -1082,7 +1082,7 @@
         <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
         <v>1.95</v>
@@ -1097,10 +1097,10 @@
         <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="O5" t="n">
         <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.93</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>3.28</v>
+        <v>2.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.62</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>3.38</v>
+        <v>2.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="U19" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.28</v>
       </c>
       <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.05</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
         <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P32" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q34" t="n">
         <v>2.45</v>
       </c>
-      <c r="O34" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R34" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U34" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>4.15</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.86</v>
+        <v>5.8</v>
       </c>
       <c r="R37" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="S37" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="T37" t="n">
-        <v>2.93</v>
+        <v>3.54</v>
       </c>
       <c r="U37" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O38" t="n">
-        <v>4.15</v>
+        <v>3.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>2.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.8</v>
+        <v>2.86</v>
       </c>
       <c r="R38" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="S38" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.54</v>
+        <v>2.93</v>
       </c>
       <c r="U38" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="V38" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6776,55 +6776,55 @@
         <v>4.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7094,55 +7094,55 @@
         <v>2.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7721,31 +7721,31 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R46" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S46" t="n">
         <v>1.32</v>
       </c>
       <c r="T46" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U46" t="n">
         <v>2.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W46" t="n">
         <v>1.07</v>
@@ -7757,7 +7757,7 @@
         <v>1.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="AA46" t="n">
         <v>1.69</v>
@@ -7766,7 +7766,7 @@
         <v>2.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AD46" t="n">
         <v>1.36</v>
@@ -7775,10 +7775,10 @@
         <v>1.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.55</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>2.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.43</v>
+        <v>3.53</v>
       </c>
       <c r="R3" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>5.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.27</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.53</v>
+        <v>5.43</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.34</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P18" t="n">
-        <v>4.33</v>
+        <v>3.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.11</v>
+        <v>2.84</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.16</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>2.11</v>
       </c>
       <c r="R20" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>4.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4865,7 +4865,7 @@
         <v>2.64</v>
       </c>
       <c r="P28" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.45</v>
       </c>
-      <c r="O36" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,31 +6290,31 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>4.21</v>
       </c>
       <c r="O37" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.8</v>
+        <v>4.61</v>
       </c>
       <c r="R37" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T37" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U37" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V37" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
@@ -6323,31 +6323,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>1.18</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="O38" t="n">
         <v>3.08</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O41" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="P41" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7724,10 +7724,10 @@
         <v>2.01</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="P46" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
         <v>2.58</v>
@@ -7736,7 +7736,7 @@
         <v>2.19</v>
       </c>
       <c r="S46" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T46" t="n">
         <v>3.12</v>
@@ -7751,16 +7751,16 @@
         <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z46" t="n">
         <v>4.02</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB46" t="n">
         <v>2.1</v>
@@ -7769,7 +7769,7 @@
         <v>2.73</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE46" t="n">
         <v>1.1</v>
@@ -7778,7 +7778,7 @@
         <v>1.62</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O47" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P47" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU47"/>
+  <dimension ref="A1:AU48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46193.4375</v>
+        <v>46193.41666666666</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46193.45833333334</v>
+        <v>46193.4375</v>
       </c>
     </row>
     <row r="19">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P20" t="n">
-        <v>4.33</v>
+        <v>3.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.11</v>
+        <v>2.84</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.16</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.86</v>
+        <v>4.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="R21" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.62</v>
+        <v>4.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>13.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="U22" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46193.5</v>
+        <v>46193.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
         <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="P28" t="n">
         <v>2.54</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46193.6875</v>
+        <v>46193.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="P32" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="R32" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S32" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="T32" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="V32" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE32" t="n">
         <v>1.01</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.28</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46193.70833333334</v>
+        <v>46193.6875</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,68 +5650,68 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46193.77083333334</v>
+        <v>46193.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46193.79166666666</v>
+        <v>46193.77083333334</v>
       </c>
     </row>
     <row r="35">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q35" t="n">
         <v>2.45</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R35" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U35" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6243,12 +6243,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46193.83333333334</v>
+        <v>46193.79166666666</v>
       </c>
     </row>
     <row r="38">
@@ -6452,10 +6452,10 @@
         <v>2.23</v>
       </c>
       <c r="O38" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="Q38" t="n">
         <v>2.86</v>
@@ -6464,10 +6464,10 @@
         <v>2.06</v>
       </c>
       <c r="S38" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T38" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U38" t="n">
         <v>2.92</v>
@@ -6491,10 +6491,10 @@
         <v>1.93</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="AD38" t="n">
         <v>1.25</v>
@@ -6506,7 +6506,7 @@
         <v>1.72</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="O39" t="n">
         <v>4.15</v>
@@ -6641,13 +6641,13 @@
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
         <v>2.12</v>
@@ -6659,13 +6659,13 @@
         <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
         <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>1.69</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.6</v>
+        <v>4.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="S40" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="T40" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="U40" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="V40" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.15</v>
+        <v>2.59</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46193.85416666666</v>
+        <v>46193.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="O41" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="P41" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="R41" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="S41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V41" t="n">
         <v>1.27</v>
       </c>
-      <c r="T41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.49</v>
-      </c>
       <c r="W41" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE41" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46193.875</v>
+        <v>46193.85416666666</v>
       </c>
     </row>
     <row r="42">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,68 +7240,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46193.89583333334</v>
+        <v>46193.875</v>
       </c>
     </row>
     <row r="44">
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="P44" t="n">
         <v>2.45</v>
@@ -7457,7 +7457,7 @@
         <v>1.08</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG44" t="n">
         <v>2.07</v>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46193.95833333334</v>
+        <v>46193.89583333334</v>
       </c>
     </row>
     <row r="46">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,80 +7721,80 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="O46" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="R46" t="n">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="S46" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T46" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U46" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="V46" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
         <v>1.01</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z46" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK46" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46193.97916666666</v>
+        <v>46193.95833333334</v>
       </c>
     </row>
     <row r="47">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P47" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q47" t="n">
         <v>2.41</v>
@@ -7901,10 +7901,10 @@
         <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V47" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
         <v>1.1</v>
@@ -7919,16 +7919,16 @@
         <v>4.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE47" t="n">
         <v>1.14</v>
@@ -7983,6 +7983,165 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
+        <v>46193.97916666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="3" t="n">
         <v>46193.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="P35" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S35" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.45</v>
       </c>
-      <c r="O36" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U36" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,31 +6608,31 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.55</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="R39" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="S39" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T39" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W39" t="n">
         <v>1.08</v>
@@ -6641,31 +6641,31 @@
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,31 +6767,31 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>5.55</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P40" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.45</v>
+        <v>5.55</v>
       </c>
       <c r="R40" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="S40" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T40" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U40" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W40" t="n">
         <v>1.08</v>
@@ -6800,47 +6800,47 @@
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P47" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="R47" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S47" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U47" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="AA47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF47" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB47" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG47" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="O48" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P48" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="R48" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S48" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T48" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U48" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V48" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1682,10 +1682,10 @@
         <v>2.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="P8" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2636,19 +2636,19 @@
         <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="P14" t="n">
         <v>3.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
         <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
         <v>2.75</v>
@@ -2666,31 +2666,31 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
         <v>1.69</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>3.38</v>
+        <v>2.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.4</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.05</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="T22" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V22" t="n">
         <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.6</v>
+        <v>3.98</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5360,10 +5360,10 @@
         <v>3.92</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
         <v>1.06</v>
@@ -5409,7 +5409,7 @@
         <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5504,19 +5504,19 @@
         <v>3.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="S32" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="U32" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="V32" t="n">
         <v>1.22</v>
@@ -5525,34 +5525,34 @@
         <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5657,61 +5657,61 @@
         <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="P33" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="R33" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S33" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="T33" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE33" t="n">
         <v>1.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q35" t="n">
         <v>2.45</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.96</v>
-      </c>
       <c r="R35" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.5</v>
       </c>
-      <c r="U35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W35" t="n">
+      <c r="AB35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.05</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,80 +6131,80 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="O36" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T36" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="AF36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK36" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>2.95</v>
+        <v>1.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.86</v>
+        <v>4.45</v>
       </c>
       <c r="R38" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="S38" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U38" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,31 +6608,31 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>5.55</v>
       </c>
       <c r="O39" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P39" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.45</v>
+        <v>5.55</v>
       </c>
       <c r="R39" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="S39" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
         <v>1.08</v>
@@ -6641,47 +6641,47 @@
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.55</v>
+        <v>2.23</v>
       </c>
       <c r="O40" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.55</v>
+        <v>2.86</v>
       </c>
       <c r="R40" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="S40" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="T40" t="n">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.62</v>
+        <v>3.32</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="O41" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R41" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="S41" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T41" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U41" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V41" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AB41" t="n">
         <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AD41" t="n">
         <v>1.16</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S42" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="T42" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="V42" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
         <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AD42" t="n">
         <v>1.15</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK42" t="n">
         <v>1.44</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P47" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="R47" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S47" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T47" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V47" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P48" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="R48" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S48" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U48" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="AA48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF48" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB48" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG48" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P2" t="n">
-        <v>3.46</v>
+        <v>2.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA2" t="n">
         <v>1.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.28</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
         <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.55</v>
+        <v>2.19</v>
       </c>
       <c r="O4" t="n">
-        <v>4.15</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.43</v>
+        <v>2.71</v>
       </c>
       <c r="R4" t="n">
-        <v>2.39</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.59</v>
+        <v>2.93</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2000,77 +2000,77 @@
         <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
         <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.86</v>
+        <v>5.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.41</v>
       </c>
-      <c r="U20" t="n">
-        <v>3.2</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.63</v>
+        <v>4.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.4</v>
+        <v>2.61</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.05</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>4.33</v>
+        <v>2.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="U21" t="n">
-        <v>2.29</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5345,7 +5345,7 @@
         <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="R31" t="n">
         <v>1.91</v>
@@ -5363,7 +5363,7 @@
         <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.06</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="O35" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="P35" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S35" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="P36" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.42</v>
       </c>
-      <c r="T36" t="n">
+      <c r="Z36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2.5</v>
       </c>
-      <c r="U36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF36" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG36" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6449,31 +6449,31 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.45</v>
+        <v>5.29</v>
       </c>
       <c r="R38" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S38" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T38" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="U38" t="n">
         <v>2.38</v>
       </c>
       <c r="V38" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
@@ -6482,31 +6482,31 @@
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE38" t="n">
         <v>1.12</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,31 +6608,31 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="O39" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S39" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W39" t="n">
         <v>1.08</v>
@@ -6641,13 +6641,13 @@
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
         <v>4.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
         <v>2.12</v>
@@ -6665,7 +6665,7 @@
         <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6767,34 +6767,34 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="R40" t="n">
         <v>2.06</v>
       </c>
       <c r="S40" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="U40" t="n">
         <v>2.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
         <v>1.01</v>
@@ -6809,7 +6809,7 @@
         <v>1.93</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
         <v>3.32</v>
@@ -6818,13 +6818,13 @@
         <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF40" t="n">
         <v>1.72</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK40" t="n">
         <v>1.53</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="P42" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.22</v>
+        <v>2.18</v>
       </c>
       <c r="R42" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="S42" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>3.34</v>
+        <v>2.36</v>
       </c>
       <c r="V42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.25</v>
       </c>
-      <c r="W42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,65 +7244,65 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="R43" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="S43" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U43" t="n">
-        <v>2.36</v>
+        <v>3.34</v>
       </c>
       <c r="V43" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="O45" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P45" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="R45" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S45" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T45" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="U45" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V45" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7721,31 +7721,31 @@
         </is>
       </c>
       <c r="N46" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R46" t="n">
         <v>2.45</v>
       </c>
-      <c r="O46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2.43</v>
-      </c>
       <c r="S46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T46" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U46" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W46" t="n">
         <v>1.12</v>
@@ -7754,31 +7754,31 @@
         <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="AD46" t="n">
         <v>1.53</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O47" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="P47" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="R47" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF47" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB47" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG47" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O48" t="n">
         <v>3.45</v>
       </c>
       <c r="P48" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="R48" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="S48" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T48" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V48" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>2.19</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.17</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
         <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.19</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.71</v>
+        <v>5.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
         <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.23</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.21</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.05</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>2.23</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="P20" t="n">
-        <v>5.5</v>
+        <v>3.21</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R20" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.4</v>
-      </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.61</v>
+        <v>3.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>2.54</v>
       </c>
       <c r="P28" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,68 +5014,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6449,19 +6449,19 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="O38" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.29</v>
+        <v>5.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
         <v>1.25</v>
@@ -6476,7 +6476,7 @@
         <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
@@ -6488,10 +6488,10 @@
         <v>4.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC38" t="n">
         <v>2.52</v>
@@ -6503,10 +6503,10 @@
         <v>1.12</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.85</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.5</v>
+        <v>2.84</v>
       </c>
       <c r="R39" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="U39" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="V39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.53</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB40" t="n">
         <v>2.12</v>
       </c>
-      <c r="O40" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="AC40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.38</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="O42" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.18</v>
+        <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="S42" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>2.36</v>
+        <v>3.34</v>
       </c>
       <c r="V42" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.64</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="P43" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>2.18</v>
       </c>
       <c r="R43" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="S43" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="T43" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U43" t="n">
-        <v>3.34</v>
+        <v>2.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.45</v>
+        <v>1.64</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>3.65</v>
@@ -7730,10 +7730,10 @@
         <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="R46" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S46" t="n">
         <v>1.24</v>
@@ -7763,16 +7763,16 @@
         <v>1.51</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AD46" t="n">
         <v>1.53</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF46" t="n">
         <v>1.44</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AK46" t="n">
         <v>1.4</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O47" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S47" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T47" t="n">
         <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK47" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="O48" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="P48" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R48" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S48" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T48" t="n">
         <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.23</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>3.21</v>
+        <v>5.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.05</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P21" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
         <v>2.88</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.63</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>2.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="O35" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="R35" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.42</v>
       </c>
-      <c r="T35" t="n">
+      <c r="Z35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.5</v>
       </c>
-      <c r="U35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF35" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG35" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="O36" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,34 +6449,34 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.95</v>
+        <v>5.55</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P38" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T38" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="U38" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
@@ -6485,44 +6485,44 @@
         <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA38" t="n">
         <v>1.64</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>4.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T39" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="U39" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.32</v>
+        <v>2.52</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.55</v>
+        <v>2.14</v>
       </c>
       <c r="O40" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.3</v>
+        <v>2.84</v>
       </c>
       <c r="R40" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="S40" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T40" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="U40" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.62</v>
+        <v>3.32</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>2.18</v>
       </c>
       <c r="R43" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="S43" t="n">
         <v>1.29</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="P47" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T47" t="n">
         <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,80 +8039,80 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="O48" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P48" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R48" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S48" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T48" t="n">
         <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="V48" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z48" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.66</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.19</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>5.17</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
         <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>2.19</v>
       </c>
       <c r="O4" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.17</v>
+        <v>2.71</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
         <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC20" t="n">
         <v>4</v>
       </c>
-      <c r="P20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.61</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="O35" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="P35" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6131,46 +6131,46 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T36" t="n">
         <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V36" t="n">
         <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB36" t="n">
         <v>1.66</v>
@@ -6188,7 +6188,7 @@
         <v>1.79</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P37" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AB37" t="n">
         <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5.55</v>
+        <v>2.14</v>
       </c>
       <c r="O38" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.3</v>
+        <v>2.84</v>
       </c>
       <c r="R38" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="S38" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T38" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="U38" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="V38" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.62</v>
+        <v>3.32</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.14</v>
+        <v>5.55</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.84</v>
+        <v>5.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.38</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="O47" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R47" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S47" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T47" t="n">
         <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="O48" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="P48" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R48" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S48" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T48" t="n">
         <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W48" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
         <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
@@ -755,19 +755,19 @@
         <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
         <v>2.38</v>
@@ -779,10 +779,10 @@
         <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -884,34 +884,34 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.97</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="P3" t="n">
         <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S3" t="n">
         <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -926,22 +926,22 @@
         <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
         <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.82</v>
@@ -1058,40 +1058,40 @@
         <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
         <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
         <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AB4" t="n">
         <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
         <v>1.08</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
         <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="R5" t="n">
         <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
         <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1235,7 +1235,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
         <v>3.28</v>
@@ -1247,19 +1247,19 @@
         <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
         <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
         <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T10" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="U10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AD10" t="n">
         <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
         <v>1.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" t="n">
         <v>1.6</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.31</v>
+        <v>2.59</v>
       </c>
       <c r="R14" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.46</v>
       </c>
       <c r="AE19" t="n">
         <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3755,19 +3755,19 @@
         <v>3.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
         <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
         <v>1.28</v>
@@ -3776,34 +3776,34 @@
         <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
         <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
         <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O23" t="n">
         <v>6.1</v>
@@ -4073,19 +4073,19 @@
         <v>13.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
         <v>2.6</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
         <v>1.48</v>
@@ -4097,31 +4097,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
         <v>4.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
         <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE23" t="n">
         <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK23" t="n">
         <v>4.14</v>
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
         <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4715,16 +4715,16 @@
         <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="U27" t="n">
         <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W27" t="n">
         <v>1.25</v>
@@ -4733,25 +4733,25 @@
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF27" t="n">
         <v>1.62</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
         <v>2.22</v>
@@ -5219,7 +5219,7 @@
         <v>2.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
         <v>5.75</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5501,46 +5501,46 @@
         <v>3.02</v>
       </c>
       <c r="P32" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="S32" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T32" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
         <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AB32" t="n">
         <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD32" t="n">
         <v>1.13</v>
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5657,61 +5657,61 @@
         <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="P33" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="R33" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.53</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC33" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE33" t="n">
         <v>1.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="O35" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="P35" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6131,16 +6131,16 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="O36" t="n">
         <v>3.15</v>
       </c>
       <c r="P36" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
@@ -6185,10 +6185,10 @@
         <v>1.06</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,19 +6290,19 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="O37" t="n">
         <v>3.15</v>
       </c>
       <c r="P37" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q37" t="n">
         <v>2.45</v>
       </c>
       <c r="R37" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S37" t="n">
         <v>1.44</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>4.95</v>
       </c>
       <c r="O38" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.64</v>
+        <v>1.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T38" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="U38" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.29</v>
+        <v>4.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.32</v>
+        <v>2.52</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.95</v>
+        <v>2.14</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.1</v>
+        <v>2.84</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.25</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="AE39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.53</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5.55</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="P40" t="n">
         <v>1.4</v>
@@ -6935,22 +6935,22 @@
         <v>3.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
         <v>2.12</v>
       </c>
       <c r="S41" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T41" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="U41" t="n">
         <v>3.05</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
@@ -6959,31 +6959,31 @@
         <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD41" t="n">
         <v>1.16</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF41" t="n">
         <v>1.95</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P42" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
         <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S42" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U42" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W42" t="n">
         <v>1.03</v>
       </c>
       <c r="X42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7265,13 +7265,13 @@
         <v>3.25</v>
       </c>
       <c r="U43" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V43" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
         <v>1.02</v>
@@ -7301,7 +7301,7 @@
         <v>1.63</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7736,10 +7736,10 @@
         <v>2.4</v>
       </c>
       <c r="S46" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T46" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U46" t="n">
         <v>2.3</v>
@@ -7772,7 +7772,7 @@
         <v>1.53</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF46" t="n">
         <v>1.44</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P47" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T47" t="n">
         <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O48" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P48" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R48" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S48" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T48" t="n">
         <v>3.18</v>
       </c>
       <c r="U48" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="V48" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z48" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF48" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU48"/>
+  <dimension ref="A1:AU47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,10 +734,10 @@
         <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S2" t="n">
         <v>1.25</v>
@@ -749,7 +749,7 @@
         <v>2.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
         <v>1.14</v>
@@ -761,7 +761,7 @@
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.57</v>
@@ -770,10 +770,10 @@
         <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1.15</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,61 +884,61 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.97</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
         <v>2.08</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>5.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.71</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>3.66</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>1.33</v>
@@ -1226,10 +1226,10 @@
         <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1259,7 +1259,7 @@
         <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
         <v>2.3</v>
       </c>
       <c r="O8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P8" t="n">
         <v>3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
         <v>2.67</v>
@@ -2024,7 +2024,7 @@
         <v>1.67</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
@@ -2039,7 +2039,7 @@
         <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
         <v>2.07</v>
@@ -2048,7 +2048,7 @@
         <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
         <v>1.4</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2109,27 +2109,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46193.375</v>
+        <v>46193.39583333334</v>
       </c>
     </row>
     <row r="12">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2427,27 +2427,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46193.39583333334</v>
+        <v>46193.41666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2633,52 +2633,52 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O14" t="n">
         <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.31</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
         <v>1.19</v>
@@ -2687,10 +2687,10 @@
         <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3063,27 +3063,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46193.41666666666</v>
+        <v>46193.4375</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46193.4375</v>
+        <v>46193.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46193.45833333334</v>
+        <v>46193.5</v>
       </c>
     </row>
     <row r="22">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S22" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
         <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46193.45833333334</v>
+        <v>46193.5</v>
       </c>
     </row>
     <row r="23">
@@ -4067,10 +4067,10 @@
         <v>1.21</v>
       </c>
       <c r="O23" t="n">
-        <v>6.1</v>
+        <v>5.98</v>
       </c>
       <c r="P23" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="Q23" t="n">
         <v>1.6</v>
@@ -4079,13 +4079,13 @@
         <v>2.6</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
         <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
         <v>1.48</v>
@@ -4097,7 +4097,7 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
         <v>4.1</v>
@@ -4106,19 +4106,19 @@
         <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
         <v>1.67</v>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46193.5</v>
+        <v>46193.52083333334</v>
       </c>
     </row>
     <row r="25">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46193.52083333334</v>
+        <v>46193.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.28</v>
+        <v>1.16</v>
       </c>
       <c r="O26" t="n">
-        <v>3.34</v>
+        <v>6.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.96</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.68</v>
+        <v>7.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>3.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.88</v>
+        <v>1.71</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>2.07</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46193.60416666666</v>
+        <v>46193.625</v>
       </c>
     </row>
     <row r="27">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,68 +4696,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>6.65</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>9.199999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.24</v>
+        <v>3.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46193.625</v>
+        <v>46193.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,84 +4855,84 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="O28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.63</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>46193.64583333334</v>
+        <v>46193.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5332,68 +5332,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46193.66666666666</v>
+        <v>46193.6875</v>
       </c>
     </row>
     <row r="32">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2.05</v>
       </c>
-      <c r="O32" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46193.6875</v>
+        <v>46193.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5650,68 +5650,68 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46193.70833333334</v>
+        <v>46193.77083333334</v>
       </c>
     </row>
     <row r="34">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5809,17 +5809,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46193.77083333334</v>
+        <v>46193.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
         <v>3.15</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S36" t="n">
         <v>1.44</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
         <v>3.2</v>
       </c>
       <c r="V36" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6243,12 +6243,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,81 +6290,81 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="O37" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>3.9</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="R37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AA37" t="n">
         <v>1.93</v>
       </c>
-      <c r="S37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AB37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK37" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AL37" t="n">
         <v>0</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46193.79166666666</v>
+        <v>46193.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="P39" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.84</v>
+        <v>5.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S39" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="U39" t="n">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
         <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="O40" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="S40" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="T40" t="n">
-        <v>3.64</v>
+        <v>2.41</v>
       </c>
       <c r="U40" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.08</v>
+        <v>1.71</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46193.83333333334</v>
+        <v>46193.85416666666</v>
       </c>
     </row>
     <row r="41">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,31 +6926,31 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P41" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="R41" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="S41" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T41" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="U41" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="V41" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
@@ -6959,31 +6959,31 @@
         <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB41" t="n">
         <v>1.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46193.85416666666</v>
+        <v>46193.875</v>
       </c>
     </row>
     <row r="42">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="O42" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.22</v>
+        <v>2.18</v>
       </c>
       <c r="R42" t="n">
-        <v>1.87</v>
+        <v>2.44</v>
       </c>
       <c r="S42" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="T42" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="V42" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.92</v>
+        <v>2.56</v>
       </c>
       <c r="AD42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,68 +7240,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46193.875</v>
+        <v>46193.89583333334</v>
       </c>
     </row>
     <row r="44">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46193.89583333334</v>
+        <v>46193.95833333334</v>
       </c>
     </row>
     <row r="46">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,80 +7721,80 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="O46" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P46" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="R46" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.22</v>
       </c>
-      <c r="T46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AK46" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46193.95833333334</v>
+        <v>46193.97916666666</v>
       </c>
     </row>
     <row r="47">
@@ -7983,165 +7983,6 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46193.97916666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R48" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" s="3" t="n">
         <v>46193.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="O18" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG18" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.49</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.32</v>
+        <v>1.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.26</v>
+        <v>5.98</v>
       </c>
       <c r="P22" t="n">
-        <v>3.05</v>
+        <v>14.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="S22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.44</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.52</v>
+        <v>4.12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.84</v>
+        <v>5.3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S37" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T37" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="U37" t="n">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG37" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.95</v>
+        <v>2.14</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>2.84</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.25</v>
       </c>
-      <c r="T38" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="AE38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.53</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,34 +6608,34 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
@@ -6644,28 +6644,28 @@
         <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA39" t="n">
         <v>1.64</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="O41" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="P41" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.22</v>
+        <v>2.18</v>
       </c>
       <c r="R41" t="n">
-        <v>1.87</v>
+        <v>2.44</v>
       </c>
       <c r="S41" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="T41" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="V41" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.92</v>
+        <v>2.56</v>
       </c>
       <c r="AD41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK41" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="P42" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.18</v>
+        <v>3.22</v>
       </c>
       <c r="R42" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="S42" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="U42" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="V42" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.56</v>
+        <v>3.92</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R46" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S46" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T46" t="n">
         <v>3.18</v>
       </c>
       <c r="U46" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="V46" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.49</v>
+        <v>2.73</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>1.22</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O47" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R47" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S47" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T47" t="n">
         <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.15</v>
+        <v>5.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
         <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.55</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.71</v>
       </c>
       <c r="R4" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
         <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="O14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.2</v>
       </c>
-      <c r="P14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.62</v>
-      </c>
       <c r="U14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.95</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.49</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>3.79</v>
       </c>
       <c r="P28" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>1.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="O34" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AB34" t="n">
         <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="O36" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AB36" t="n">
         <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O46" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R46" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S46" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T46" t="n">
         <v>3.18</v>
       </c>
       <c r="U46" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="V46" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF46" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>1.22</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P47" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T47" t="n">
         <v>3.18</v>
       </c>
       <c r="U47" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W47" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.49</v>
+        <v>2.73</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -734,25 +734,25 @@
         <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
         <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -767,13 +767,13 @@
         <v>1.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
         <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
         <v>1.15</v>
@@ -798,7 +798,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.55</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>3.86</v>
+        <v>3.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
         <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>5.17</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.71</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="Q5" t="n">
         <v>3.66</v>
@@ -1226,7 +1226,7 @@
         <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
@@ -1247,7 +1247,7 @@
         <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
@@ -1275,7 +1275,7 @@
         <v>1.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1682,10 +1682,10 @@
         <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>2.67</v>
       </c>
       <c r="R10" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
         <v>1.21</v>
@@ -2021,7 +2021,7 @@
         <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
         <v>1.17</v>
@@ -2030,7 +2030,7 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
         <v>5.4</v>
@@ -2048,13 +2048,13 @@
         <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
         <v>1.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="U13" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.01</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
         <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,34 +3269,34 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="O18" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P18" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
@@ -3305,28 +3305,28 @@
         <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
         <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
         <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>1.49</v>
@@ -3449,10 +3449,10 @@
         <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
@@ -3461,10 +3461,10 @@
         <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
         <v>2.31</v>
@@ -3479,13 +3479,13 @@
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
         <v>3.26</v>
       </c>
       <c r="P21" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
         <v>2.9</v>
@@ -3767,13 +3767,13 @@
         <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V21" t="n">
         <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
@@ -3785,7 +3785,7 @@
         <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
         <v>1.62</v>
@@ -3803,7 +3803,7 @@
         <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="O22" t="n">
-        <v>5.98</v>
+        <v>5.9</v>
       </c>
       <c r="P22" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="Q22" t="n">
         <v>1.6</v>
@@ -3938,13 +3938,13 @@
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
         <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
         <v>2.19</v>
@@ -3959,7 +3959,7 @@
         <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG22" t="n">
         <v>1.67</v>
@@ -3978,7 +3978,7 @@
         <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
         <v>3.34</v>
@@ -4391,55 +4391,55 @@
         <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.96</v>
+        <v>3.72</v>
       </c>
       <c r="R25" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S25" t="n">
         <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK25" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O26" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="P26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>1.5</v>
@@ -4568,16 +4568,16 @@
         <v>1.93</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.24</v>
@@ -4586,16 +4586,16 @@
         <v>3.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
         <v>2.1</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
         <v>4</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="O27" t="n">
         <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
         <v>2.6</v>
@@ -5192,13 +5192,13 @@
         <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
         <v>1.18</v>
@@ -5222,7 +5222,7 @@
         <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AD30" t="n">
         <v>1.12</v>
@@ -5234,7 +5234,7 @@
         <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
         <v>1.91</v>
@@ -5336,43 +5336,43 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O31" t="n">
         <v>3.02</v>
       </c>
       <c r="P31" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S31" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AA31" t="n">
         <v>2.62</v>
@@ -5381,19 +5381,19 @@
         <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5495,49 +5495,49 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="O32" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S32" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T32" t="n">
         <v>2.39</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z32" t="n">
         <v>2.46</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC32" t="n">
         <v>4.7</v>
@@ -5546,13 +5546,13 @@
         <v>1.12</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="O34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P34" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>1.44</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
         <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>5</v>
+        <v>3.74</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>1.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="O35" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S35" t="n">
         <v>1.44</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U35" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="V35" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.72</v>
+        <v>4.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.17</v>
       </c>
       <c r="O37" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.3</v>
+        <v>2.93</v>
       </c>
       <c r="R37" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="S37" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="T37" t="n">
-        <v>3.64</v>
+        <v>2.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="V37" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.62</v>
+        <v>3.58</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,61 +6449,61 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>5</v>
       </c>
       <c r="O38" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="P38" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.84</v>
+        <v>5.76</v>
       </c>
       <c r="R38" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="T38" t="n">
-        <v>2.93</v>
+        <v>3.74</v>
       </c>
       <c r="U38" t="n">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.29</v>
+        <v>4.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.32</v>
+        <v>2.49</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG38" t="n">
         <v>2</v>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.95</v>
+        <v>4.35</v>
       </c>
       <c r="O39" t="n">
         <v>4</v>
@@ -6623,40 +6623,40 @@
         <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T39" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U39" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
         <v>2.16</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE39" t="n">
         <v>1.18</v>
@@ -6665,7 +6665,7 @@
         <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK39" t="n">
         <v>1.1</v>
@@ -6767,19 +6767,19 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R40" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="S40" t="n">
         <v>1.46</v>
@@ -6788,7 +6788,7 @@
         <v>2.41</v>
       </c>
       <c r="U40" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
         <v>1.3</v>
@@ -6797,16 +6797,16 @@
         <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
         <v>1.6</v>
@@ -6818,13 +6818,13 @@
         <v>1.16</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,22 +6926,22 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="O41" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P41" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R41" t="n">
         <v>2.44</v>
       </c>
       <c r="S41" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T41" t="n">
         <v>3.25</v>
@@ -6953,37 +6953,37 @@
         <v>1.53</v>
       </c>
       <c r="W41" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB41" t="n">
         <v>2.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>1.18</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7085,55 +7085,55 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P42" t="n">
         <v>2.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S42" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T42" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="V42" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
         <v>1.04</v>
@@ -7142,7 +7142,7 @@
         <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,68 +7240,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7565,10 +7565,10 @@
         <v>2.55</v>
       </c>
       <c r="O45" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
         <v>3.08</v>
@@ -7577,49 +7577,49 @@
         <v>2.4</v>
       </c>
       <c r="S45" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T45" t="n">
         <v>3.75</v>
       </c>
       <c r="U45" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V45" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
         <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF45" t="n">
         <v>1.44</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7721,34 +7721,34 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
         <v>3.55</v>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R46" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T46" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U46" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V46" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
@@ -7772,7 +7772,7 @@
         <v>1.42</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF46" t="n">
         <v>1.55</v>
@@ -7883,28 +7883,28 @@
         <v>2.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R47" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S47" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T47" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U47" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W47" t="n">
         <v>1.07</v>
@@ -7913,25 +7913,25 @@
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AD47" t="n">
         <v>1.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF47" t="n">
         <v>1.62</v>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.05</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,65 +3587,65 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>2.97</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.43</v>
+        <v>4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG20" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="O21" t="n">
-        <v>3.26</v>
+        <v>5.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>13.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="S21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.44</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.52</v>
+        <v>4.04</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>5.9</v>
+        <v>3.26</v>
       </c>
       <c r="P22" t="n">
-        <v>13.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="S22" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.43</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.04</v>
+        <v>1.52</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
         <v>3.34</v>
@@ -4397,10 +4397,10 @@
         <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
         <v>2.3</v>
@@ -4412,7 +4412,7 @@
         <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
         <v>1.16</v>
@@ -4421,7 +4421,7 @@
         <v>4.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB25" t="n">
         <v>2.2</v>
@@ -4430,10 +4430,10 @@
         <v>2.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF25" t="n">
         <v>1.55</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>3.79</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.63</v>
+        <v>2.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.63</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S34" t="n">
         <v>1.44</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="V34" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="R35" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
         <v>1.44</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.17</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.93</v>
+        <v>5.76</v>
       </c>
       <c r="R37" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="T37" t="n">
-        <v>2.56</v>
+        <v>3.74</v>
       </c>
       <c r="U37" t="n">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.88</v>
+        <v>4.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.58</v>
+        <v>2.49</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="O38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.76</v>
+        <v>5.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="T38" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="U38" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.45</v>
+        <v>4.32</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.35</v>
+        <v>2.17</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.1</v>
+        <v>2.93</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="S39" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T39" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.32</v>
+        <v>2.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,68 +7240,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="P46" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R46" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S46" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T46" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U46" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="V46" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W46" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O47" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="P47" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R47" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T47" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U47" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="V47" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z47" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF47" t="n">
+      <c r="AK47" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="P16" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="S16" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="U16" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.99</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
         <v>1.01</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4.33</v>
+        <v>2.97</v>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG19" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,65 +3587,65 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="U20" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.44</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG22" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O23" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.25</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB23" t="n">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,68 +4855,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>2.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>2.17</v>
       </c>
       <c r="O37" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.76</v>
+        <v>2.93</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="S37" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="T37" t="n">
-        <v>3.74</v>
+        <v>2.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V37" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.49</v>
+        <v>3.58</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P38" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>5.76</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="T38" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="U38" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V38" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.17</v>
+        <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.64</v>
+        <v>1.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.93</v>
+        <v>5.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T39" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="U39" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.88</v>
+        <v>4.32</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P41" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="S41" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U41" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="V41" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="W41" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.61</v>
+        <v>3.78</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="R42" t="n">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="S42" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.78</v>
+        <v>2.61</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,80 +7721,80 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="P46" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R46" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S46" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T46" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U46" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="V46" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF46" t="n">
+      <c r="AK46" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="P47" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S47" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T47" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U47" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="V47" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>3.43</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.12</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="P18" t="n">
-        <v>6.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="O19" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG19" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
         <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.25</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB22" t="n">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="O23" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.44</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AE23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4855,68 +4855,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.63</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P35" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6140,13 +6140,13 @@
         <v>2.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
         <v>2.5</v>
@@ -6167,7 +6167,7 @@
         <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
         <v>2.08</v>
@@ -6185,7 +6185,7 @@
         <v>1.06</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
         <v>1.83</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.17</v>
+        <v>4.35</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>1.52</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.93</v>
+        <v>5.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T37" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.88</v>
+        <v>4.32</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.76</v>
+        <v>2.93</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="S38" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="T38" t="n">
-        <v>3.74</v>
+        <v>2.56</v>
       </c>
       <c r="U38" t="n">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V38" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.49</v>
+        <v>3.58</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG38" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P39" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.1</v>
+        <v>5.76</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="T39" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="U39" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="R41" t="n">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="S41" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="T41" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="V41" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W41" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.78</v>
+        <v>2.61</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P42" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="S42" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="T42" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="V42" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="W42" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.61</v>
+        <v>3.78</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="P46" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R46" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S46" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T46" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U46" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="V46" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W46" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O47" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="P47" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R47" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T47" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U47" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="V47" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z47" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF47" t="n">
+      <c r="AK47" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
         <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
         <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG17" t="n">
         <v>1.78</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="O19" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.43</v>
       </c>
       <c r="AD19" t="n">
         <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="P20" t="n">
-        <v>6.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>13.9</v>
+        <v>2.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.6</v>
+        <v>3.18</v>
       </c>
       <c r="R21" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="S21" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.43</v>
+        <v>3.78</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>4.04</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>1.13</v>
       </c>
       <c r="O22" t="n">
-        <v>3.26</v>
+        <v>7.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="S22" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U22" t="n">
-        <v>3.18</v>
+        <v>2.33</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.01</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.16</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.52</v>
+        <v>3.05</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S24" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
         <v>1.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.26</v>
+        <v>2.78</v>
       </c>
       <c r="O27" t="n">
         <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R28" t="n">
         <v>1.84</v>
       </c>
       <c r="S28" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="T28" t="n">
         <v>2.3</v>
@@ -4889,16 +4889,16 @@
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB28" t="n">
         <v>1.4</v>
@@ -4910,7 +4910,7 @@
         <v>1.12</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF28" t="n">
         <v>2.3</v>
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>3.02</v>
@@ -5345,55 +5345,55 @@
         <v>3.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R31" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="S31" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="V31" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
         <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5495,43 +5495,43 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S32" t="n">
         <v>1.53</v>
       </c>
       <c r="T32" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="U32" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA32" t="n">
         <v>2.41</v>
@@ -5540,7 +5540,7 @@
         <v>1.49</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AD32" t="n">
         <v>1.12</v>
@@ -5549,10 +5549,10 @@
         <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="O34" t="n">
         <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O35" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,80 +6131,80 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P36" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK36" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,80 +6290,80 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P37" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.1</v>
+        <v>5.76</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="T37" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="U37" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V37" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK37" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>4.35</v>
       </c>
       <c r="O38" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.64</v>
+        <v>1.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.93</v>
+        <v>5.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T38" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="U38" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="V38" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.88</v>
+        <v>4.32</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>2.17</v>
       </c>
       <c r="O39" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.76</v>
+        <v>2.93</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="S39" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="T39" t="n">
-        <v>3.74</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="V39" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.49</v>
+        <v>3.58</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6767,22 +6767,22 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" t="n">
         <v>2.63</v>
       </c>
       <c r="R40" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S40" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T40" t="n">
         <v>2.41</v>
@@ -6800,25 +6800,25 @@
         <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB40" t="n">
         <v>1.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD40" t="n">
         <v>1.16</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF40" t="n">
         <v>1.93</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7085,31 +7085,31 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
         <v>1.89</v>
       </c>
       <c r="S42" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
         <v>2.9</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
         <v>1.04</v>
@@ -7118,31 +7118,31 @@
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF42" t="n">
         <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -725,34 +725,34 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S2" t="n">
         <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,13 +761,13 @@
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC2" t="n">
         <v>2.45</v>
@@ -798,7 +798,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>4.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.17</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.78</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.11</v>
@@ -1217,10 +1217,10 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U5" t="n">
         <v>2.79</v>
@@ -1229,22 +1229,22 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
         <v>3.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC5" t="n">
         <v>3.2</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2.95</v>
       </c>
       <c r="O7" t="n">
-        <v>12.5</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>28</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="W10" t="n">
         <v>1.17</v>
@@ -2030,31 +2030,31 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>4.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.12</v>
+        <v>4.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
         <v>3.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.03</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AF13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG18" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="O19" t="n">
         <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S19" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
         <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,65 +3587,65 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R20" t="n">
         <v>2.4</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.39</v>
+        <v>2.55</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>3.28</v>
       </c>
       <c r="U21" t="n">
-        <v>3.04</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.78</v>
+        <v>2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O23" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="T23" t="n">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.31</v>
+        <v>3.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.7</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
         <v>3.72</v>
@@ -4397,19 +4397,19 @@
         <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
         <v>1.03</v>
@@ -4430,10 +4430,10 @@
         <v>2.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF25" t="n">
         <v>1.55</v>
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>8.460000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T26" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="U26" t="n">
         <v>1.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -4577,7 +4577,7 @@
         <v>1.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA26" t="n">
         <v>1.24</v>
@@ -4586,16 +4586,16 @@
         <v>3.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AE26" t="n">
         <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG26" t="n">
         <v>2.1</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="n">
         <v>4</v>
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="O27" t="n">
         <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4868,16 +4868,16 @@
         <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="S28" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
         <v>3.75</v>
@@ -4889,13 +4889,13 @@
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y28" t="n">
         <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
         <v>2.6</v>
@@ -4907,7 +4907,7 @@
         <v>6.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE28" t="n">
         <v>1.04</v>
@@ -4916,7 +4916,7 @@
         <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.07</v>
+        <v>2.35</v>
       </c>
       <c r="R34" t="n">
         <v>2</v>
       </c>
       <c r="S34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V34" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF34" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG34" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>4.45</v>
+        <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O36" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="O37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.76</v>
+        <v>5.1</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V37" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
         <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG37" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.35</v>
+        <v>5.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P38" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.1</v>
+        <v>5.43</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T38" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="V38" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W38" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
         <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="O39" t="n">
         <v>3.2</v>
@@ -6653,7 +6653,7 @@
         <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="AD39" t="n">
         <v>1.25</v>
@@ -6662,10 +6662,10 @@
         <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK39" t="n">
         <v>1.5</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="S41" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="T41" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U41" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="V41" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z41" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE41" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="R42" t="n">
-        <v>1.89</v>
+        <v>2.47</v>
       </c>
       <c r="S42" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U42" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="V42" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,68 +7240,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
         <v>3.08</v>
@@ -7580,13 +7580,13 @@
         <v>1.23</v>
       </c>
       <c r="T45" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U45" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W45" t="n">
         <v>1.14</v>
@@ -7598,22 +7598,22 @@
         <v>1.15</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF45" t="n">
         <v>1.44</v>
@@ -7635,7 +7635,7 @@
         <v>1.29</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,80 +7721,80 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P46" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="Q46" t="n">
         <v>2.6</v>
       </c>
       <c r="R46" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S46" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T46" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U46" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V46" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK46" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="O47" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="P47" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S47" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T47" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U47" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="V47" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -705,23 +705,23 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '52', '90+4']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46193.08333333334</v>
@@ -864,23 +864,23 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '36', '43', '71']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46193.16666666666</v>
@@ -1020,26 +1020,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '67']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46193.16666666666</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
         <v>3.66</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
         <v>1.38</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2.95</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="P14" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC14" t="n">
-        <v>6.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
         <v>1.53</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="S16" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
         <v>1.53</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.95</v>
+        <v>2.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.58</v>
+        <v>2.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,52 +3428,52 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>6.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
         <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
         <v>1.43</v>
@@ -3482,10 +3482,10 @@
         <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>6.39</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.83</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>7.14</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>2.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.55</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.33</v>
+        <v>3.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.33</v>
+        <v>2.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>3.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>1.13</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>7.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.79</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="S23" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.81</v>
+        <v>4.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>2.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>2.9</v>
+        <v>3.79</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>4.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>4.45</v>
+        <v>2.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,68 +7240,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/jogos_2026-06-20.xlsx
+++ b/jogos_2026-06-20.xlsx
@@ -852,139 +852,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['32', '67']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>['35', '36', '43', '71']</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>0.49</v>
+        <v>2.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.36</v>
+        <v>0.63</v>
       </c>
       <c r="AS3" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="AT3" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46193.16666666666</v>
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['35', '36', '43', '71']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['32', '67']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>19</v>
-      </c>
       <c r="AP4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.38</v>
+        <v>0.49</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.63</v>
+        <v>2.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="AT4" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46193.16666666666</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1191,14 +1191,14 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46193.26041666666</v>
@@ -1319,149 +1319,149 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.95</v>
+        <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.56</v>
+        <v>1.22</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '24', '27', '30', '39', '69', '72', '90']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46193.29166666666</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,37 +1590,37 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46193.29166666666</v>
@@ -1656,33 +1656,33 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
         <v>2.85</v>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '79', '83']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '13', '65']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46193.33333333334</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="O11" t="n">
         <v>4.05</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.78</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.02</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.6</v>
+        <v>2.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.24</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="T14" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.4</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.95</v>
+        <v>6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O16" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="S16" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.08</v>
       </c>
-      <c r="U16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.99</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.05</v>
+        <v>3.68</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>6.39</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.83</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.3</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.98</v>
+        <v>2.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
         <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,34 +3905,34 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S22" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
@@ -3941,25 +3941,25 @@
         <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
         <v>1.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
         <v>1.87</v>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4067,31 +4067,31 @@
         <v>1.13</v>
       </c>
       <c r="O23" t="n">
-        <v>7.14</v>
+        <v>6.2</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>1.55</v>
       </c>
       <c r="R23" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
@@ -4100,44 +4100,44 @@
         <v>1.17</v>
       </c>
       <c r="Z23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK23" t="n">
         <v>4.33</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>3.05</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>3.79</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,17 +5014,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5173,68 +5173,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5816,61 +5816,61 @@
         <v>1.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>4.45</v>
+        <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="